--- a/PRJ13797_SPI_Calculator.xlsx
+++ b/PRJ13797_SPI_Calculator.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="SPI Calculator" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="JMUX PV Examples" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Step-by-Step Guide" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="EV &amp; PV Deep Dive" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="JMUX PV Examples" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Step-by-Step Guide" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="30">
+  <fonts count="57">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -169,8 +170,164 @@
       <color rgb="002563EB"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E293B"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="007C3AED"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="007C3AED"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00374151"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0016A34A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0016A34A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="002563EB"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E3A5F"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="007C3AED"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00DC2626"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="0016A34A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0016A34A"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00EA580C"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00EA580C"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
@@ -227,8 +384,48 @@
         <fgColor rgb="00F1F5F9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007C3AED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F3FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDE9FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAFAFA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0016A34A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0FDF4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DC2626"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -264,11 +461,88 @@
         <color rgb="001E3A5F"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="001E3A5F"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="001E3A5F"/>
+      </right>
+      <top style="medium">
+        <color rgb="001E3A5F"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="001E3A5F"/>
+      </right>
+      <top style="medium">
+        <color rgb="001E3A5F"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="001E3A5F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -402,6 +676,148 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1037,10 +1453,12 @@
           <t>YOUR OVERALL SPI:</t>
         </is>
       </c>
+      <c r="B22" s="45" t="n"/>
       <c r="C22" s="15">
         <f>IF(B20=0,"Enter values above",C20/B20)</f>
         <v/>
       </c>
+      <c r="D22" s="45" t="n"/>
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="14" t="inlineStr">
@@ -1048,10 +1466,12 @@
           <t>STATUS:</t>
         </is>
       </c>
+      <c r="B23" s="45" t="n"/>
       <c r="C23" s="16">
         <f>IF(B20=0,"—",IF(C22&gt;1.1,"🔵 AHEAD OF SCHEDULE",IF(C22&gt;=0.9,"🟢 ON TRACK",IF(C22&gt;=0.7,"🟡 YELLOW — MONITOR",IF(C22&gt;=0.5,"🟠 ORANGE — ACT NOW","🔴 CRITICAL — ESCALATE")))))</f>
         <v/>
       </c>
+      <c r="D23" s="45" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="17" t="inlineStr">
@@ -1066,11 +1486,13 @@
           <t>Above 1.10</t>
         </is>
       </c>
+      <c r="B26" s="46" t="n"/>
       <c r="C26" s="18" t="inlineStr">
         <is>
           <t>🔵 Ahead of Schedule</t>
         </is>
       </c>
+      <c r="D26" s="46" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="19" t="inlineStr">
@@ -1078,11 +1500,13 @@
           <t>0.90 – 1.10</t>
         </is>
       </c>
+      <c r="B27" s="46" t="n"/>
       <c r="C27" s="19" t="inlineStr">
         <is>
           <t>🟢 On Track</t>
         </is>
       </c>
+      <c r="D27" s="46" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="20" t="inlineStr">
@@ -1090,11 +1514,13 @@
           <t>0.70 – 0.90</t>
         </is>
       </c>
+      <c r="B28" s="46" t="n"/>
       <c r="C28" s="20" t="inlineStr">
         <is>
           <t>🟡 Yellow — Monitor Closely</t>
         </is>
       </c>
+      <c r="D28" s="46" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="21" t="inlineStr">
@@ -1102,11 +1528,13 @@
           <t>0.50 – 0.70</t>
         </is>
       </c>
+      <c r="B29" s="46" t="n"/>
       <c r="C29" s="21" t="inlineStr">
         <is>
           <t>🟠 Orange — Action Required</t>
         </is>
       </c>
+      <c r="D29" s="46" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="22" t="inlineStr">
@@ -1114,11 +1542,13 @@
           <t>Below 0.50</t>
         </is>
       </c>
+      <c r="B30" s="46" t="n"/>
       <c r="C30" s="22" t="inlineStr">
         <is>
           <t>🔴 Critical — Escalate to CIO/SVP</t>
         </is>
       </c>
+      <c r="D30" s="46" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="21">
@@ -1154,6 +1584,676 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="47" t="inlineStr">
+        <is>
+          <t>EV &amp; PV DEEP DIVE — How to Calculate Planned Value &amp; Earned Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="48" t="inlineStr">
+        <is>
+          <t>Using real milestones from PRJ13797 JMUX Replacement — PSEG Long Island</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="49" t="inlineStr">
+        <is>
+          <t>SECTION 1:  WHAT IS PLANNED VALUE (PV)?</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="50" t="inlineStr">
+        <is>
+          <t>PV = the budgeted cost (or milestone weight) of ALL work scheduled to be completed by a specific date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="51" t="inlineStr">
+        <is>
+          <t>Think of PV as your PROMISE to management. It's what your project schedule SAID would be done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="52" t="inlineStr">
+        <is>
+          <t>3 WAYS TO ASSIGN PV VALUE — Choose ONE method and stick with it</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="53" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="B9" s="53" t="inlineStr">
+        <is>
+          <t>METHOD 1: Milestone Count
+(Simplest ✅ Used on JMUX)</t>
+        </is>
+      </c>
+      <c r="C9" s="53" t="inlineStr">
+        <is>
+          <t>METHOD 2: Percentage Weight
+(Best for mixed-size tasks)</t>
+        </is>
+      </c>
+      <c r="D9" s="53" t="inlineStr">
+        <is>
+          <t>METHOD 3: Dollar Value
+(Best for budget tracking)</t>
+        </is>
+      </c>
+      <c r="E9" s="53" t="inlineStr">
+        <is>
+          <t>JMUX Used This?</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="54" t="inlineStr">
+        <is>
+          <t>BGP Design Approved</t>
+        </is>
+      </c>
+      <c r="B10" s="55" t="inlineStr">
+        <is>
+          <t>1 milestone = 1</t>
+        </is>
+      </c>
+      <c r="C10" s="56" t="inlineStr">
+        <is>
+          <t>20% of network tasks</t>
+        </is>
+      </c>
+      <c r="D10" s="56" t="inlineStr">
+        <is>
+          <t>$25,000 (BGP design fee)</t>
+        </is>
+      </c>
+      <c r="E10" s="57" t="inlineStr">
+        <is>
+          <t>✅ Method 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="58" t="inlineStr">
+        <is>
+          <t>Northport DC Power Complete</t>
+        </is>
+      </c>
+      <c r="B11" s="59" t="inlineStr">
+        <is>
+          <t>1 milestone = 1</t>
+        </is>
+      </c>
+      <c r="C11" s="60" t="inlineStr">
+        <is>
+          <t>10% of infra tasks</t>
+        </is>
+      </c>
+      <c r="D11" s="60" t="inlineStr">
+        <is>
+          <t>$18,000 (power install)</t>
+        </is>
+      </c>
+      <c r="E11" s="61" t="inlineStr">
+        <is>
+          <t>✅ Method 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="54" t="inlineStr">
+        <is>
+          <t>OTDR Test — Hicksville Link</t>
+        </is>
+      </c>
+      <c r="B12" s="55" t="inlineStr">
+        <is>
+          <t>1 milestone = 1</t>
+        </is>
+      </c>
+      <c r="C12" s="56" t="inlineStr">
+        <is>
+          <t>15% of testing tasks</t>
+        </is>
+      </c>
+      <c r="D12" s="56" t="inlineStr">
+        <is>
+          <t>$8,500 (testing labor)</t>
+        </is>
+      </c>
+      <c r="E12" s="57" t="inlineStr">
+        <is>
+          <t>✅ Method 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="58" t="inlineStr">
+        <is>
+          <t>NSP Fiber Run &amp; Terminated</t>
+        </is>
+      </c>
+      <c r="B13" s="59" t="inlineStr">
+        <is>
+          <t>1 milestone = 1</t>
+        </is>
+      </c>
+      <c r="C13" s="60" t="inlineStr">
+        <is>
+          <t>25% of cabling tasks</t>
+        </is>
+      </c>
+      <c r="D13" s="60" t="inlineStr">
+        <is>
+          <t>$12,000 (Hawkeye labor)</t>
+        </is>
+      </c>
+      <c r="E13" s="61" t="inlineStr">
+        <is>
+          <t>✅ Method 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="54" t="inlineStr">
+        <is>
+          <t>Phase 2 IFR Packages x3</t>
+        </is>
+      </c>
+      <c r="B14" s="55" t="inlineStr">
+        <is>
+          <t>1 milestone = 1</t>
+        </is>
+      </c>
+      <c r="C14" s="56" t="inlineStr">
+        <is>
+          <t>30% of design tasks</t>
+        </is>
+      </c>
+      <c r="D14" s="56" t="inlineStr">
+        <is>
+          <t>$45,000 (BMcD design fee)</t>
+        </is>
+      </c>
+      <c r="E14" s="57" t="inlineStr">
+        <is>
+          <t>✅ Method 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="62" t="inlineStr">
+        <is>
+          <t>TOTAL PV</t>
+        </is>
+      </c>
+      <c r="B15" s="62" t="inlineStr">
+        <is>
+          <t>PV = 5  (5 milestones)</t>
+        </is>
+      </c>
+      <c r="C15" s="62" t="inlineStr">
+        <is>
+          <t>PV = 100%</t>
+        </is>
+      </c>
+      <c r="D15" s="62" t="inlineStr">
+        <is>
+          <t>PV = $108,500</t>
+        </is>
+      </c>
+      <c r="E15" s="63" t="inlineStr"/>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="64" t="inlineStr">
+        <is>
+          <t>SECTION 2:  WHAT IS EARNED VALUE (EV)?</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="65" t="inlineStr">
+        <is>
+          <t>EV = the budgeted value of work ACTUALLY completed to date. You only earn value when a task is DONE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="66" t="inlineStr">
+        <is>
+          <t>Think of EV as your SCORECARD. It's what you actually earned based on real completed work — not effort or time spent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="67" t="inlineStr">
+        <is>
+          <t>THE GOLDEN RULES OF EV — Critical for accurate SPI</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="68" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B22" s="69" t="inlineStr">
+        <is>
+          <t>RULE 1: 0% or 100% only (Binary Method)</t>
+        </is>
+      </c>
+      <c r="C22" s="70" t="inlineStr">
+        <is>
+          <t>A task is either DONE or NOT DONE. No partial credit.
+If BGP execution is 80% complete — EV = 0 until it's fully done.</t>
+        </is>
+      </c>
+      <c r="D22" s="71" t="inlineStr">
+        <is>
+          <t>JMUX Feb 2026: Northport ILO was blocked. It was 0% — EV = 0, not 0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="68" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B23" s="69" t="inlineStr">
+        <is>
+          <t>RULE 2: Use the SAME unit as PV</t>
+        </is>
+      </c>
+      <c r="C23" s="70" t="inlineStr">
+        <is>
+          <t>If PV uses milestones, EV counts completed milestones.
+If PV uses dollars, EV uses the budgeted dollar value of completed work.</t>
+        </is>
+      </c>
+      <c r="D23" s="71" t="inlineStr">
+        <is>
+          <t>JMUX uses milestone count (1 per task). 3 done out of 5 = EV of 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="68" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B24" s="69" t="inlineStr">
+        <is>
+          <t>RULE 3: EV is based on PLANNED value — not actual cost</t>
+        </is>
+      </c>
+      <c r="C24" s="70" t="inlineStr">
+        <is>
+          <t>If a task was planned at $25K and you completed it spending $30K,
+EV is still $25K. Actual cost is tracked separately (CPI, not SPI).</t>
+        </is>
+      </c>
+      <c r="D24" s="71" t="inlineStr">
+        <is>
+          <t>JMUX: BGP design budgeted at $25K. Regardless of actual spend, EV = $25K when done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="52" customHeight="1">
+      <c r="A25" s="68" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B25" s="69" t="inlineStr">
+        <is>
+          <t>RULE 4: EV can never exceed PV for a task</t>
+        </is>
+      </c>
+      <c r="C25" s="70" t="inlineStr">
+        <is>
+          <t>You cannot earn more than what was planned.
+Doing extra work that wasn't planned does NOT increase EV.</t>
+        </is>
+      </c>
+      <c r="D25" s="71" t="inlineStr">
+        <is>
+          <t>JMUX: Hawkeye moved Phase 2 equipment early. Not in PV — so EV = 0 for that task.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="72" t="inlineStr">
+        <is>
+          <t>SECTION 3:  FULL WORKED EXAMPLE — February 2026 (JMUX PRJ13797)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="73" t="inlineStr">
+        <is>
+          <t>Scenario: End of February 2026. You need to report SPI to the CIO. Here is exactly how to do it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="74" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B29" s="74" t="inlineStr">
+        <is>
+          <t>Planned Milestone</t>
+        </is>
+      </c>
+      <c r="C29" s="74" t="inlineStr">
+        <is>
+          <t>PV Value
+(assigned at start)</t>
+        </is>
+      </c>
+      <c r="D29" s="74" t="inlineStr">
+        <is>
+          <t>Completed?
+(honest answer)</t>
+        </is>
+      </c>
+      <c r="E29" s="74" t="inlineStr">
+        <is>
+          <t>EV Earned
+(only if 100% done)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="B30" s="54" t="inlineStr">
+        <is>
+          <t>Northport ILO port configuration complete</t>
+        </is>
+      </c>
+      <c r="C30" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="77" t="inlineStr">
+        <is>
+          <t>❌ NO — DC power fuse tripping blocked all ILO work</t>
+        </is>
+      </c>
+      <c r="E30" s="78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="79" t="n">
+        <v>2</v>
+      </c>
+      <c r="B31" s="80" t="inlineStr">
+        <is>
+          <t>OTDR test — Hicksville to Syosset link active</t>
+        </is>
+      </c>
+      <c r="C31" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="82" t="inlineStr">
+        <is>
+          <t>✅ YES — Bad filter replaced. Link confirmed active.</t>
+        </is>
+      </c>
+      <c r="E31" s="83" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="75" t="n">
+        <v>3</v>
+      </c>
+      <c r="B32" s="54" t="inlineStr">
+        <is>
+          <t>NSP fiber cable run &amp; terminated at Hicksville</t>
+        </is>
+      </c>
+      <c r="C32" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="82" t="inlineStr">
+        <is>
+          <t>✅ YES — Hawkeye completed fiber run to NSP rack.</t>
+        </is>
+      </c>
+      <c r="E32" s="83" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="79" t="n">
+        <v>4</v>
+      </c>
+      <c r="B33" s="80" t="inlineStr">
+        <is>
+          <t>Phase 2 IFRs — Far Rockaway, Valley Stream, Cedarhurst</t>
+        </is>
+      </c>
+      <c r="C33" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="82" t="inlineStr">
+        <is>
+          <t>✅ YES — Burns &amp; McDonnell submitted all 3 packages.</t>
+        </is>
+      </c>
+      <c r="E33" s="83" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" s="84" t="inlineStr">
+        <is>
+          <t>TOTALS</t>
+        </is>
+      </c>
+      <c r="C34" s="85" t="inlineStr">
+        <is>
+          <t>PV = 4</t>
+        </is>
+      </c>
+      <c r="D34" s="86" t="inlineStr">
+        <is>
+          <t>3 tasks completed ✅   |   1 task blocked ❌</t>
+        </is>
+      </c>
+      <c r="E34" s="87" t="inlineStr">
+        <is>
+          <t>EV = 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="88" t="inlineStr">
+        <is>
+          <t>SPI CALCULATION:</t>
+        </is>
+      </c>
+      <c r="C35" s="89" t="inlineStr">
+        <is>
+          <t>SPI  =  EV ÷ PV  =  3 ÷ 4  =  0.75   →   🟠 ORANGE — Action Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="90" t="inlineStr">
+        <is>
+          <t>SECTION 4:  COMMON MISTAKES — What NOT to Do</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="52" customHeight="1">
+      <c r="A38" s="91" t="inlineStr">
+        <is>
+          <t>❌ Mistake 1</t>
+        </is>
+      </c>
+      <c r="B38" s="92" t="inlineStr">
+        <is>
+          <t>Giving partial EV credit</t>
+        </is>
+      </c>
+      <c r="C38" s="70" t="inlineStr">
+        <is>
+          <t>Saying 'ILO is 50% done so EV = 0.5' — WRONG.
+EV is 0 until the task is fully complete.</t>
+        </is>
+      </c>
+      <c r="D38" s="71" t="inlineStr">
+        <is>
+          <t>JMUX: ILO blocked in Feb. EV = 0, not 0.5. That honesty is what flagged the schedule risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="52" customHeight="1">
+      <c r="A39" s="91" t="inlineStr">
+        <is>
+          <t>❌ Mistake 2</t>
+        </is>
+      </c>
+      <c r="B39" s="92" t="inlineStr">
+        <is>
+          <t>Counting effort instead of output</t>
+        </is>
+      </c>
+      <c r="C39" s="70" t="inlineStr">
+        <is>
+          <t>Saying 'we worked 40 hours on BGP so we earned 0.5' — WRONG.
+EV is about deliverables completed, not hours spent.</t>
+        </is>
+      </c>
+      <c r="D39" s="71" t="inlineStr">
+        <is>
+          <t>JMUX: Hawkeye spent weeks on NSP wiring. EV = 0 until fiber was run AND terminated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="52" customHeight="1">
+      <c r="A40" s="91" t="inlineStr">
+        <is>
+          <t>❌ Mistake 3</t>
+        </is>
+      </c>
+      <c r="B40" s="92" t="inlineStr">
+        <is>
+          <t>Changing PV mid-project without approval</t>
+        </is>
+      </c>
+      <c r="C40" s="70" t="inlineStr">
+        <is>
+          <t>Reducing PV to make SPI look better is data manipulation.
+If scope changes, get formal change control approval first.</t>
+        </is>
+      </c>
+      <c r="D40" s="71" t="inlineStr">
+        <is>
+          <t>JMUX: If ILO was removed from PV without a change request, SPI would look artificially good.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="52" customHeight="1">
+      <c r="A41" s="91" t="inlineStr">
+        <is>
+          <t>❌ Mistake 4</t>
+        </is>
+      </c>
+      <c r="B41" s="92" t="inlineStr">
+        <is>
+          <t>Not updating EV regularly</t>
+        </is>
+      </c>
+      <c r="C41" s="70" t="inlineStr">
+        <is>
+          <t>SPI is only useful if updated consistently — weekly or monthly.
+Stale data gives stale decisions.</t>
+        </is>
+      </c>
+      <c r="D41" s="71" t="inlineStr">
+        <is>
+          <t>JMUX: Jay updates SPI monthly for CIO reporting. Weekly for internal team tracking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="93" t="inlineStr">
+        <is>
+          <t>PRJ13797 JMUX Replacement — PSEG Long Island  |  PM: Jay Gunaratne  |  Built by Sachi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="28">
+    <mergeCell ref="C23"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="C24"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="C25"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="C22"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="C35:E35"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1184,6 +2284,10 @@
           <t>JANUARY 2026 — On Track</t>
         </is>
       </c>
+      <c r="B4" s="94" t="n"/>
+      <c r="C4" s="94" t="n"/>
+      <c r="D4" s="94" t="n"/>
+      <c r="E4" s="46" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="26" t="inlineStr">
@@ -1308,7 +2412,6 @@
       <c r="E10" s="30" t="inlineStr"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" s="19" t="inlineStr">
         <is>
           <t>TOTAL</t>
@@ -1336,6 +2439,10 @@
           <t>FEBRUARY 2026 — Northport DC Power Issue</t>
         </is>
       </c>
+      <c r="B13" s="94" t="n"/>
+      <c r="C13" s="94" t="n"/>
+      <c r="D13" s="94" t="n"/>
+      <c r="E13" s="46" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
@@ -1457,7 +2564,6 @@
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" t="inlineStr"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
           <t>TOTAL</t>
@@ -1485,6 +2591,10 @@
           <t>MARCH 2026 — Recovery Underway</t>
         </is>
       </c>
+      <c r="B21" s="94" t="n"/>
+      <c r="C21" s="94" t="n"/>
+      <c r="D21" s="94" t="n"/>
+      <c r="E21" s="46" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
@@ -1629,7 +2739,6 @@
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" t="inlineStr"/>
       <c r="B28" s="20" t="inlineStr">
         <is>
           <t>TOTAL</t>
@@ -1671,7 +2780,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1705,7 +2814,6 @@
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" s="42" t="inlineStr">
         <is>
           <t>What did your schedule say should be DONE by the end of this month?
@@ -1731,7 +2839,6 @@
       </c>
     </row>
     <row r="7" ht="45" customHeight="1">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" s="42" t="inlineStr">
         <is>
           <t>Give each task a number. On JMUX we use 1 per milestone.
@@ -1757,7 +2864,6 @@
       </c>
     </row>
     <row r="10" ht="45" customHeight="1">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" s="42" t="inlineStr">
         <is>
           <t>PV = Planned Value = the total of all milestone values you planned to complete.</t>
@@ -1782,7 +2888,6 @@
       </c>
     </row>
     <row r="13" ht="45" customHeight="1">
-      <c r="A13" t="inlineStr"/>
       <c r="B13" s="42" t="inlineStr">
         <is>
           <t>Check each milestone. Did it actually get completed this period?
@@ -1808,7 +2913,6 @@
       </c>
     </row>
     <row r="16" ht="45" customHeight="1">
-      <c r="A16" t="inlineStr"/>
       <c r="B16" s="42" t="inlineStr">
         <is>
           <t>EV = Earned Value = total value of work ACTUALLY completed.</t>
@@ -1833,7 +2937,6 @@
       </c>
     </row>
     <row r="19" ht="45" customHeight="1">
-      <c r="A19" t="inlineStr"/>
       <c r="B19" s="42" t="inlineStr">
         <is>
           <t>That's it. The formula is simple. The hard part is being honest about what's done.</t>
